--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>136104557</v>
       </c>
       <c r="B55" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>136106452</v>
       </c>
       <c r="B56" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136106502</v>
       </c>
       <c r="B57" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
